--- a/important_mails_2026-09-12.xlsx
+++ b/important_mails_2026-09-12.xlsx
@@ -1175,7 +1175,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>付款/资金类</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1190,69 +1190,21 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Sat, 5 Sep 2026 09:20:41 +0000</t>
+          <t>Fri, 11 Sep 2026 14:52:08 +0000</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+          <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>FBA reimbursement notification</t>
+          <t>Discover sessions built for growing businesses, and save $200</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfillment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfillment center. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.com/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.com/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
-- T</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 11 Sep 2026 14:52:08 +0000</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Discover sessions built for growing businesses, and save $200</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-10/7z5qrws/6883537229/h/8hGIqk3myHUPoHwg1cA2VFOh0rQM9Qk9zX-mp3ce36Q)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5qrww/6883537229/h/8hGIqk3myHUPoHwg1cA2VFOh0rQM9Qk9zX-mp3ce36Q)
@@ -1265,39 +1217,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 12:33:05 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1317,39 +1269,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 12:27:50 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1366,39 +1318,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 14:22:12 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1422,39 +1374,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 13:24:25 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>New sessions on AI, brand building, and account health</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-04/7z5l4fj/6879091625/h/N9M90HPlPpU67n4uE_mKTweCIMAyiYf9R4WAB4ShsLU)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5l4fm/6879091625/h/N9M90HPlPpU67n4uE_mKTweCIMAyiYf9R4WAB4ShsLU)
@@ -1470,39 +1422,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 12:29:09 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Grow your Amazon business this September—$200 off registration</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-03/7z5kmdj/6877034516/h/rztcP4y8gTis_yypujjYm1jG3dK9ZVpI_qeU8WzLMjQ)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5kmdm/6877034516/h/rztcP4y8gTis_yypujjYm1jG3dK9ZVpI_qeU8WzLMjQ)
@@ -1517,39 +1469,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 13:43:26 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1569,143 +1521,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 5 Sep 2026 14:14:20 +0000</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>✅ Transparency Payment Confirmed!</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello,
-Thank you for your purchase! Your payment has been successfully processed. Here is your payment summary:
-Invoice Number: 1LH6-Q1GT-XPX4...
-Hello,
-Thank you for your purchase! Your payment has been successfully processed. Here is your payment summary:
-Invoice Number: 1LH6-Q1GT-XPX4
-Date: September 5, 2026
-Amount Paid: 76.00 USD
-Remaining Balance: 0.00 USD
-Payment Method: Cash Transfer
-You can access all your billing and payments related information by going to your Transactions Dashboard.
- [Link to invoice Dashboard]
- If you see an 'Access Denied' error message when you use the link below and are not able to access the invoice/credit note, then please email transparency-support@amazon.com with your profile link (see instructions below).
- Frequently Asked Questions (FAQ)
- I see 'Access Denied' message after logging into the Transparency Portal, what should I do?
-- Please log into your Amazon.com account associated with this email address. If you don't have an account, please create one with this email address.
-- Go to https://www.amazon.com/profile.
-- Copy the URL that was generated in the search bar. The profile link you need to provide will look similar to this: https://</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 5 Sep 2026 12:11:55 +0000</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>1:1 expert access, new AI tools, and $200 off—register now</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-03/7z5kmcf/6873229782/h/qYVDW02XHhfOyfe1KqLK6R5PsXDPD3YirAthddzc8II)
-[Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5kmcj/6873229782/h/qYVDW02XHhfOyfe1KqLK6R5PsXDPD3YirAthddzc8II)
-What's waiting for you at Accelerate
-Whether you're looking to sharpen your strategy, interact with new tools, or connect with experts who know your category, Accelerate gives you three days to invest directly in your business. Last year, 4 out of 5 attendees left feeling more confident in growing their business.
-Accelerate is just weeks away, September 22–24 in Seattle, and we have a limited-time offer for you: save $200 and register for just $399 with code FLASH200 at checkout.
-Supplies are limited, so don't wait—offer ends September 15.
-[Register now](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5kmcj/6873229782/h/qYVDW02XHhfOyfe1KqLK6R5PsXDPD3YirAthddzc8II)
-"I got to talk to the actual product managers who build the tools I use every day."
-2025 Attendee
-Here's what's waiting for you:
-- 1:1 expert access at Seller Café: Bring your biggest challenge </t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 15:50:06 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -1727,39 +1575,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 18:07:39 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -1777,39 +1625,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 15:09:01 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1827,39 +1675,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 08:06:37 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1877,39 +1725,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 17:08:09 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1927,39 +1775,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 18:07:40 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -1977,39 +1825,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 18:06:40 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -2028,39 +1876,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 17:40:10 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Your VAT invoice for EPR Pay on Behalf charges for Amazon.fr sales</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Votre facture pour les frais de paiement au titre de la REP pour les ventes sur Amazon.fr |
 Your VAT invoice for EPR Pay on Behalf charges for Amazon.fr sales
@@ -2073,39 +1921,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 17:07:27 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -2124,39 +1972,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 17:07:04 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2174,39 +2022,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 13:08:31 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -2223,39 +2071,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 20:59:58 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2273,39 +2121,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 20:39:32 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2323,87 +2171,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 5 Sep 2026 13:13:54 +0000</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon-Fulfilled Inventory - Action Required</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Dear Seller,
-You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
-Please create a removal request for the ASIN(s) listed below to have your inventory sent to a location of your choice. If this inventory is not removed within 30 days of this notification (by 04/10/2026), we shall dispose of it in accordance with our FBA policies.
-For more information regarding the removal of this product, see the notification e-mail you received from our Seller Performance Team.
-Thank you for your prompt attention to this matter.
-Yours faithfully,
-Fulfilment by Amazon Team
-Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
-Affected Product(s):
-B0GYPZ58JY
- SPC-EUAmazon-738873502977648</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Fri, 11 Sep 2026 14:08:42 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>通过 Q4 活动拓展您的业务 — 尽早提报，节省费用</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Q4 业绩
 尊敬的卖家，
@@ -2435,39 +2235,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 03:39:41 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>"Comunicados de Amazon Seller Central (no responder)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>[Amazon.es] Hemos suprimido uno o varios de tus listings de las búsquedas en la web de Amazon</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 [Amazon.es] Hemos suprimido uno o varios de tus listings de las búsquedas en la web de Amazon
@@ -2483,39 +2283,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 16:45:36 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Transparency No Reply &lt;noreply-transparency@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>OPR 体验优化——无需再手动追踪货件  /  Improvement to Your OPR Experience — No More Manual Shipment Tracking</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>尊敬的 Crifeton 团队：
 我们很高兴地通知您，OPR（Operational Performance Review运营表现评估）流程迎来一项优化，这将使开启 OPR 变得更加简单，并且您无需再手动追踪货件。
@@ -2539,39 +2339,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 16:45:33 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Transparency No Reply &lt;noreply-transparency@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>OPR 体验优化——无需再手动追踪货件  /  Improvement to Your OPR Experience — No More Manual Shipment Tracking</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>尊敬的 Crifeton 团队：
 我们很高兴地通知您，OPR（Operational Performance Review运营表现评估）流程迎来一项优化，这将使开启 OPR 变得更加简单，并且您无需再手动追踪货件。
@@ -2595,39 +2395,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 14:40:23 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 8/2026</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 8/2026
  96
@@ -2649,39 +2449,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 22:05:50 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Envía la documentación de seguridad del producto para evitar la desactivación de los listados</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai MX:
@@ -2698,39 +2498,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 16:05:13 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Actualiza los precios de venta recomendados a más tardar el 9 de septiembre de 2026</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
  Las nuevas reglas para validar los precios de referencia entran en vigor el 9 de septiembre de 2026.
@@ -2744,39 +2544,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 09:38:25 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Ottieni la tua garanzia IVA in Italia €2.350 rimborso fino a 31 dicembre</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -2792,39 +2592,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 05:09:23 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 8/2026</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 8/2026
  96
@@ -2842,39 +2642,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 05:02:45 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnungskorrektur Verkäufer for 8/2026</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnungskorrektur Verkäufer for 8/2026
  96
@@ -2898,40 +2698,40 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 04:49:12 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Credit Note for
  8/2026</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Credit Note for 8/2026
  96
@@ -2949,39 +2749,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 04:40:19 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Kreditnota Säljare for 8/2026</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Kreditnota Säljare for 8/2026
  96
@@ -3008,39 +2808,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 04:36:05 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Kreditnota Säljare for 8/2026</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Kreditnota Säljare for 8/2026
  96
@@ -3067,39 +2867,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 04:29:13 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Nota de Crédito Vendedor for 8/2026</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Nota de Crédito Vendedor for 8/2026
  96
@@ -3126,39 +2926,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 04:28:07 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 8/2026</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 8/2026
  96
@@ -3176,39 +2976,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 04:27:11 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnungskorrektur Verkäufer for 8/2026</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnungskorrektur Verkäufer for 8/2026
  96
@@ -3232,39 +3032,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 04:09:19 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Nota de Crédito Vendedor for 8/2026</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Nota de Crédito Vendedor for 8/2026
  96
@@ -3291,39 +3091,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 03:03:01 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnungskorrektur Versand durch Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnungskorrektur Versand durch Amazon for 8/2026
  96
@@ -3346,39 +3146,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 02:03:22 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Verkoper for 8/2026</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Creditnota Verkoper for 8/2026
  96
@@ -3402,39 +3202,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 01:34:58 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 8/2026
  96
@@ -3461,39 +3261,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 01:08:53 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 8/2026</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 8/2026
  96
@@ -3511,39 +3311,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 01:06:25 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 8/2026
  96
@@ -3568,39 +3368,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 01:00:11 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 8/2026</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 8/2026
  96
@@ -3618,39 +3418,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 00:39:22 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 8/2026
  96
@@ -3674,39 +3474,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 23:59:03 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 8/2026
  96
@@ -3725,39 +3525,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 23:56:53 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 8/2026
  96
@@ -3784,39 +3584,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 23:48:47 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 8/2026
  96
@@ -3843,39 +3643,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 23:41:01 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 8/2026
  96
@@ -3900,39 +3700,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 23:09:33 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Verkäufer for 8/2026</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Verkäufer for 8/2026
  96
@@ -3957,39 +3757,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 22:41:45 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Vendedor for 8/2026</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Vendedor for 8/2026
  96
@@ -4016,39 +3816,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 22:38:15 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 8/2026
  96
@@ -4075,39 +3875,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 22:37:39 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 8/2026
  96
@@ -4131,39 +3931,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 22:25:15 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 8/2026
  96
@@ -4190,39 +3990,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 22:25:11 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 8/2026
  96
@@ -4247,39 +4047,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 22:18:55 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 8/2026
  96
@@ -4304,39 +4104,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 22:18:08 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Verkoper for 8/2026</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Verkoper for 8/2026
  96
@@ -4360,39 +4160,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 20:59:59 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Verkoper for 8/2026</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Verkoper for 8/2026
  96
@@ -4412,39 +4212,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 20:39:31 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -4460,39 +4260,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 20:29:23 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 8/2026
  96
@@ -4511,39 +4311,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 20:15:08 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 8/2026
  96
@@ -4562,39 +4362,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 19:50:44 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Sprzedawcy for 8/2026</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.pl Faktura Sprzedawcy for 8/2026
  96
@@ -4619,39 +4419,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 19:45:42 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 8/2026
  96
@@ -4678,39 +4478,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 19:11:44 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Selbstfakturierung AGL for 8/2026</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Selbstfakturierung AGL for 8/2026
  96
@@ -4735,39 +4535,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 19:06:41 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Verkäufer for 8/2026</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Verkäufer for 8/2026
  96
@@ -4792,39 +4592,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 18:35:49 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 8/2026
  96
@@ -4849,40 +4649,40 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 18:10:01 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -4900,39 +4700,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 18:08:44 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -4949,39 +4749,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 18:06:29 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -4999,39 +4799,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 17:50:58 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Realizacja przez Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Realizacja przez Amazon for 8/2026
  96
@@ -5055,39 +4855,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 17:16:06 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Vendedor for 8/2026</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Vendedor for 8/2026
  96
@@ -5114,39 +4914,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 17:08:49 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -5164,40 +4964,40 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 17:06:12 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -5215,39 +5015,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 17:05:11 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Säljare for 8/2026</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Säljare for 8/2026
  96
@@ -5274,39 +5074,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 16:47:02 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 8/2026</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 8/2026
  96
@@ -5324,39 +5124,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 15:12:47 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 8/2026
  96
@@ -5383,39 +5183,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 14:26:25 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 8/2026</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 8/2026
  96
@@ -5439,39 +5239,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 13:00:45 +0200 (CEST)</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>"no.reply@wipo.int" &lt;no.reply@wipo.int&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>WIPO Account - Recovery e-mail</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>WIPO Account - Recovery e-mail
  Dear deis DEIS,
@@ -5486,39 +5286,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 13:00:45 +0200 (CEST)</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>"no.reply@wipo.int" &lt;no.reply@wipo.int&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>WIPO Account - Recovery e-mail</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>WIPO Account - Recovery e-mail
  Dear deis DEIS,
@@ -5533,39 +5333,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 21:21:59 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -5581,40 +5381,40 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 21:08:16 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -5630,39 +5430,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 21:07:44 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -5678,39 +5478,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 20:53:24 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -5724,39 +5524,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 20:39:39 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -5772,40 +5572,40 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 20:06:48 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -5821,40 +5621,40 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Fri, 11 Sep 2026 09:43:34 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>"seller-coaching-m@amazon.com" &lt;seller-coaching-m@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>[Case ID:13247704742]"Your Help Needed" Optimize Your Next EU FBA
  Shipment Based on Inventory Health [A-AWD]</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>96
 [Case ID:13247704742]"Your Help Needed" Optimize Your Next EU FBA Shipment Based on Inventory Health [A-AWD]
@@ -5872,40 +5672,40 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 09:37:46 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>"seller-coaching-m@amazon.com" &lt;seller-coaching-m@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 13247704742] Optimize Your Next EU FBA Shipment Based on
  Inventory Health [A-AWD]</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 RE:[CASE 13247704742] Optimize Your Next EU FBA Shipment Based on Inventory Health [A-AWD]
@@ -5921,40 +5721,40 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 03:24:54 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Communications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>[Amazon.fr] One or More of Your Amazon Listings Have Been Search
  Suppressed</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
 [Amazon.fr] One or More of Your Amazon Listings Have Been Search Suppressed
@@ -5971,39 +5771,87 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 5 Sep 2026 09:20:41 +0000</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
+ Hello from Fulfillment by Amazon,
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfillment center. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.com/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.com/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+- T</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 17:54:07 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (4rjrNkqMZx)</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -6023,39 +5871,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 05:00:38 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6071,39 +5919,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Wed, 2 Sep 2026 10:49:16 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (j2jHyzbiUU)</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -6123,39 +5971,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Wed, 2 Sep 2026 04:50:31 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6171,39 +6019,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 19:31:35 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (TrF4EN0N6o)</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -6228,39 +6076,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 15:06:42 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>"dg-seller-enrollment@amazon.com" &lt;dg-seller-enrollment@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>[Case ID:21758925371]*Your Case Resolved* You’re invited to the Dangerous Goods (Hazmat) Program US</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>96
 [Case ID:21758925371]*Your Case Resolved* You’re invited to the Dangerous Goods (Hazmat) Program US
@@ -6273,39 +6121,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 05:00:11 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6321,39 +6169,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Sun, 30 Aug 2026 14:03:08 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -6374,39 +6222,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Sat, 29 Aug 2026 04:40:08 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6422,39 +6270,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Fri, 28 Aug 2026 16:34:35 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (0QNxXwzJgp)</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -6474,39 +6322,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Fri, 28 Aug 2026 15:00:25 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>"dg-seller-enrollment@amazon.com" &lt;dg-seller-enrollment@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>[Case ID:21758925371]*Your Help Needed* You’re invited to the Dangerous Goods (Hazmat) Program US</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 [Case ID:21758925371]*Your Help Needed* You’re invited to the Dangerous Goods (Hazmat) Program US
@@ -6520,39 +6368,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Fri, 28 Aug 2026 09:22:31 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6568,39 +6416,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Fri, 28 Aug 2026 04:53:03 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6616,39 +6464,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 05:02:47 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6664,39 +6512,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 23:58:41 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (0Bix9UfQE5)</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -6716,39 +6564,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 15:00:02 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>"dg-seller-enrollment@amazon.com" &lt;dg-seller-enrollment@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 21758925371] You’re invited to the Dangerous Goods (Hazmat) Program US</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 21758925371] You’re invited to the Dangerous Goods (Hazmat) Program US
@@ -6759,39 +6607,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 04:58:09 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6807,39 +6655,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 18:49:27 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (qO7a7il03F)</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -6859,39 +6707,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 12:33:42 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (aVWN9vWwFe)</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -6911,39 +6759,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 05:00:58 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6959,39 +6807,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Sun, 23 Aug 2026 14:55:04 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
 Balance paid on your Amazon seller account
@@ -7014,39 +6862,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Sun, 23 Aug 2026 14:36:21 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 Balance paid on your Amazon seller account
@@ -7064,39 +6912,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Sun, 23 Aug 2026 04:55:13 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -7112,39 +6960,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Sat, 22 Aug 2026 03:28:54 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -7160,39 +7008,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Fri, 21 Aug 2026 16:10:20 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -7213,39 +7061,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 15:24:40 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -7266,39 +7114,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 04:58:18 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -7314,39 +7162,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Wed, 19 Aug 2026 16:12:03 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -7367,39 +7215,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Tue, 18 Aug 2026 05:03:01 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -7415,39 +7263,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Mon, 17 Aug 2026 04:53:18 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -7463,39 +7311,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Sun, 16 Aug 2026 04:55:15 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -7511,39 +7359,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Sun, 16 Aug 2026 02:33:51 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (TGTg3P+M9T)</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -7568,39 +7416,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Sat, 15 Aug 2026 09:36:41 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -7616,39 +7464,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Sat, 15 Aug 2026 04:42:49 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -7664,39 +7512,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Sat, 15 Aug 2026 01:29:59 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -7717,39 +7565,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Thu, 13 Aug 2026 04:59:33 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -7765,40 +7613,144 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 5 Sep 2026 14:14:20 +0000</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>✅ Transparency Payment Confirmed!</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello,
+Thank you for your purchase! Your payment has been successfully processed. Here is your payment summary:
+Invoice Number: 1LH6-Q1GT-XPX4...
+Hello,
+Thank you for your purchase! Your payment has been successfully processed. Here is your payment summary:
+Invoice Number: 1LH6-Q1GT-XPX4
+Date: September 5, 2026
+Amount Paid: 76.00 USD
+Remaining Balance: 0.00 USD
+Payment Method: Cash Transfer
+You can access all your billing and payments related information by going to your Transactions Dashboard.
+ [Link to invoice Dashboard]
+ If you see an 'Access Denied' error message when you use the link below and are not able to access the invoice/credit note, then please email transparency-support@amazon.com with your profile link (see instructions below).
+ Frequently Asked Questions (FAQ)
+ I see 'Access Denied' message after logging into the Transparency Portal, what should I do?
+- Please log into your Amazon.com account associated with this email address. If you don't have an account, please create one with this email address.
+- Go to https://www.amazon.com/profile.
+- Copy the URL that was generated in the search bar. The profile link you need to provide will look similar to this: https://</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 5 Sep 2026 12:11:55 +0000</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>1:1 expert access, new AI tools, and $200 off—register now</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-03/7z5kmcf/6873229782/h/qYVDW02XHhfOyfe1KqLK6R5PsXDPD3YirAthddzc8II)
+[Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5kmcj/6873229782/h/qYVDW02XHhfOyfe1KqLK6R5PsXDPD3YirAthddzc8II)
+What's waiting for you at Accelerate
+Whether you're looking to sharpen your strategy, interact with new tools, or connect with experts who know your category, Accelerate gives you three days to invest directly in your business. Last year, 4 out of 5 attendees left feeling more confident in growing their business.
+Accelerate is just weeks away, September 22–24 in Seattle, and we have a limited-time offer for you: save $200 and register for just $399 with code FLASH200 at checkout.
+Supplies are limited, so don't wait—offer ends September 15.
+[Register now](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5kmcj/6873229782/h/qYVDW02XHhfOyfe1KqLK6R5PsXDPD3YirAthddzc8II)
+"I got to talk to the actual product managers who build the tools I use every day."
+2025 Attendee
+Here's what's waiting for you:
+- 1:1 expert access at Seller Café: Bring your biggest challenge </t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 15:50:39 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>A note from Katie Scott: Your spot at Amazon Accelerate 2026 is
  waiting</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-31/7z5hj9l/6869623185/h/t49nmPjAcWA0AwhOnCq47cStxvNE4bo5hge57UVyO-E)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5hj9p/6869623185/h/t49nmPjAcWA0AwhOnCq47cStxvNE4bo5hge57UVyO-E)
@@ -7812,39 +7764,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 14:51:26 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -7860,39 +7812,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 15:50:35 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -7908,39 +7860,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 15:34:38 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Three weeks out. Have you registered?</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-31/7z5hj8h/6865258013/h/R4H_C9NHvcjNXDhguSu8h5kLS8rvmJFLgxujNzlVtzg)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5hj8l/6865258013/h/R4H_C9NHvcjNXDhguSu8h5kLS8rvmJFLgxujNzlVtzg)
@@ -7954,39 +7906,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 13:47:19 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8006,39 +7958,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 13:38:54 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8055,39 +8007,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 13:38:25 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8107,39 +8059,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 10:39:58 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Envía los números de registro de RAP antes del 30 de junio</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
  You’ll be enrolled in EPR Pay on Behalf unless you provide valid Extended Producer Responsibility registration numbers by June 30
@@ -8148,39 +8100,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Sat, 29 Aug 2026 10:29:17 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Early-bird pricing ends this Saturday—Register now</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-26/7z5f1dw/6858839240/h/an0hGAbEsn_GcD7m8vCy3PA0zGSpSHw1r6FwW9L-zGQ)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5f1dz/6858839240/h/an0hGAbEsn_GcD7m8vCy3PA0zGSpSHw1r6FwW9L-zGQ)
@@ -8199,39 +8151,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Sat, 29 Aug 2026 00:42:21 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8248,39 +8200,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Sat, 29 Aug 2026 00:41:47 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8300,39 +8252,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 10:23:35 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Final Call: Early-bird pricing ends this Saturday, 8/29—Register now</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-25/7z5dp4h/6853578557/h/fMcSGqjdqgEDoIsJN08zOUUgHxkKkP49uaYlySvIDk8)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5dp4l/6853578557/h/fMcSGqjdqgEDoIsJN08zOUUgHxkKkP49uaYlySvIDk8)
@@ -8351,39 +8303,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 12:33:59 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Sellers called this one of the highlights of Accelerate</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-24/7z5dhr3/6851676170/h/Wjp-bmbnJMm0YNVflBOldr6STH8h5YJsrXHhgAzeKUo)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5dhr6/6851676170/h/Wjp-bmbnJMm0YNVflBOldr6STH8h5YJsrXHhgAzeKUo)
@@ -8399,39 +8351,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 12:24:04 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -8455,39 +8407,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Mon, 24 Aug 2026 12:38:26 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Early-bird pricing ends August 29. Save $100 now</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-19/7z596lw/6847886297/h/fajszjfN78xb3oKGP7qMLJQXUM-VqKc8irnBicIIs-Y)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z596lz/6847886297/h/fajszjfN78xb3oKGP7qMLJQXUM-VqKc8irnBicIIs-Y)
@@ -8503,39 +8455,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Sat, 22 Aug 2026 17:14:31 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8552,39 +8504,39 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Sat, 22 Aug 2026 17:14:20 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8604,39 +8556,39 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Sat, 22 Aug 2026 12:13:14 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>Early-bird pricing ends Saturday, Aug. 29—Save $100 before it's full price</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-19/7z596mz/6845766770/h/4MOe7WIB0iKog9ZJ2gooAw5JI3-zJ2xmrM13S4lZjTw)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z596n3/6845766770/h/4MOe7WIB0iKog9ZJ2gooAw5JI3-zJ2xmrM13S4lZjTw)
@@ -8652,40 +8604,40 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Fri, 21 Aug 2026 10:16:19 +0000</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>The fireside chat we teased is here. Early-bird pricing ends next
  week.</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-17/7z58bwt/6843878552/h/i5ZL7d6_GwNwKOo6-EVWTgdYbnnn0rhnWQ2kP-UgsCs)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z58bwx/6843878552/h/i5ZL7d6_GwNwKOo6-EVWTgdYbnnn0rhnWQ2kP-UgsCs)
@@ -8701,39 +8653,39 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 16:05:40 +0000</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8753,39 +8705,39 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 16:03:47 +0000</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -8802,39 +8754,39 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 16:03:34 +0000</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8854,39 +8806,39 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 12:23:03 +0000</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>You're exactly who Accelerate was designed for</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-18/7z58zcm/6842423531/h/zqV8R_k6k7yKhqDq4dX1yXmefn5JIN40lXum5Y6M4KM)
 [Your next level starts here](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z58zcq/6842423531/h/zqV8R_k6k7yKhqDq4dX1yXmefn5JIN40lXum5Y6M4KM)
@@ -8901,40 +8853,40 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Tue, 18 Aug 2026 12:13:14 +0000</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Live at Accelerate 2026: Mary Beth Westmoreland and Amit Agarwal
  fireside chat</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-17/7z58bxx/6837257199/h/ROTGYDonH0Pvpb92J9CZAGdoz2-iazjSlqoOkDG1azg)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z58by1/6837257199/h/ROTGYDonH0Pvpb92J9CZAGdoz2-iazjSlqoOkDG1azg)
@@ -8947,39 +8899,39 @@
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Mon, 17 Aug 2026 18:27:13 +0000</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8996,39 +8948,39 @@
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Mon, 17 Aug 2026 18:26:45 +0000</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9048,39 +9000,39 @@
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Sat, 15 Aug 2026 13:39:43 +0000</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9100,39 +9052,39 @@
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Sat, 15 Aug 2026 13:38:59 +0000</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9149,39 +9101,39 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 10:11:50 +0000</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9198,39 +9150,39 @@
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 10:11:23 +0000</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9250,39 +9202,39 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 07:03:07 +0000</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>您的亚马逊卖家账户支付的余额</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>96
 您的亚马逊卖家账户支付的余额
@@ -9311,40 +9263,40 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Thu, 13 Aug 2026 13:25:55 +0000</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>Did you catch Mary Beth's message? Early-bird extension ends August
  29</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-07/7z543yq/6828853872/h/09uV_tsw5XUFTzEZF_b-1pdSpEuhEDbCowtX9OlIcwk)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z543yt/6828853872/h/09uV_tsw5XUFTzEZF_b-1pdSpEuhEDbCowtX9OlIcwk)
@@ -9355,6 +9307,54 @@
 [An image showcasing the key elements of a product listing page.](https://go.amazonsellerservices.com/e/229492/watch-v-qBwS3fdidZo/7z543yx/6828853872/h/09uV_tsw5XUFTzEZF_b-1pdSpEuhEDbCowtX9OlIcwk)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z543yt/6828853872/h/09uV_tsw5XUFTzEZF_b-1pdSpEuhEDbCowtX9OlIcwk)
 This year, based on your feedback, we’ve expanded nearly every part of the conference. More interactive breakout </t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 5 Sep 2026 13:13:54 +0000</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon-Fulfilled Inventory - Action Required</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>Dear Seller,
+You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
+Please create a removal request for the ASIN(s) listed below to have your inventory sent to a location of your choice. If this inventory is not removed within 30 days of this notification (by 04/10/2026), we shall dispose of it in accordance with our FBA policies.
+For more information regarding the removal of this product, see the notification e-mail you received from our Seller Performance Team.
+Thank you for your prompt attention to this matter.
+Yours faithfully,
+Fulfilment by Amazon Team
+Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
+Affected Product(s):
+B0GYPZ58JY
+ SPC-EUAmazon-738873502977648</t>
         </is>
       </c>
     </row>
